--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-20.xlsx
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.37</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
